--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-11 20:00</t>
+          <t>更新时间: 2026-08-11 20:01</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-11 20:01</t>
+          <t>更新时间: 2026-08-12 13:30</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-12 13:30</t>
+          <t>更新时间: 2026-08-12 13:49</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-14 13:32</t>
+          <t>更新时间: 2026-08-14 13:49</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-14 16:41</t>
+          <t>更新时间: 2026-08-15 08:16</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-15 08:16</t>
+          <t>更新时间: 2026-08-15 11:09</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-15 11:09</t>
+          <t>更新时间: 2026-08-15 11:22</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-15 11:22</t>
+          <t>更新时间: 2026-08-15 12:06</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-15 13:00</t>
+          <t>更新时间: 2026-08-16 08:10</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-16 08:10</t>
+          <t>更新时间: 2026-08-16 11:29</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-16 11:29</t>
+          <t>更新时间: 2026-08-16 11:36</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-16 11:36</t>
+          <t>更新时间: 2026-08-16 12:21</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-17 11:29</t>
+          <t>更新时间: 2026-08-17 11:37</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-17 11:37</t>
+          <t>更新时间: 2026-08-17 12:27</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-17 13:53</t>
+          <t>更新时间: 2026-08-18 08:12</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-18 08:12</t>
+          <t>更新时间: 2026-08-18 11:12</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-18 13:16</t>
+          <t>更新时间: 2026-08-19 08:13</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-19 08:13</t>
+          <t>更新时间: 2026-08-19 11:15</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-20 12:22</t>
+          <t>更新时间: 2026-08-20 13:18</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-20 13:18</t>
+          <t>更新时间: 2026-08-21 11:35</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-21 11:35</t>
+          <t>更新时间: 2026-08-21 11:57</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-21 11:57</t>
+          <t>更新时间: 2026-08-21 12:24</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-21 12:24</t>
+          <t>更新时间: 2026-08-21 13:20</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-21 13:20</t>
+          <t>更新时间: 2026-08-22 08:14</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-22 11:11</t>
+          <t>更新时间: 2026-08-22 11:26</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-22 11:26</t>
+          <t>更新时间: 2026-08-22 12:17</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-23 08:12</t>
+          <t>更新时间: 2026-08-23 11:32</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-23 13:16</t>
+          <t>更新时间: 2026-08-24 08:12</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-24 08:12</t>
+          <t>更新时间: 2026-08-24 11:36</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-24 11:36</t>
+          <t>更新时间: 2026-08-24 12:06</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-24 12:06</t>
+          <t>更新时间: 2026-08-24 13:06</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-24 13:06</t>
+          <t>更新时间: 2026-08-24 13:57</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-24 13:57</t>
+          <t>更新时间: 2026-08-25 08:13</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-25 12:24</t>
+          <t>更新时间: 2026-08-25 13:48</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-25 13:48</t>
+          <t>更新时间: 2026-08-26 08:01</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-26 08:01</t>
+          <t>更新时间: 2026-08-26 09:57</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-26 09:57</t>
+          <t>更新时间: 2026-08-26 10:26</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-26 10:26</t>
+          <t>更新时间: 2026-08-26 11:29</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-26 11:29</t>
+          <t>更新时间: 2026-08-26 12:31</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-26 12:31</t>
+          <t>更新时间: 2026-08-27 12:51</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-27 12:51</t>
+          <t>更新时间: 2026-08-27 17:43</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-27 17:43</t>
+          <t>更新时间: 2026-08-27 19:05</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-27 19:05</t>
+          <t>更新时间: 2026-08-27 20:55</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-27 20:55</t>
+          <t>更新时间: 2026-08-27 22:53</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-27 22:53</t>
+          <t>更新时间: 2026-08-28 15:14</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-28 15:14</t>
+          <t>更新时间: 2026-08-28 19:20</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-28 19:20</t>
+          <t>更新时间: 2026-08-28 20:38</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-28 20:38</t>
+          <t>更新时间: 2026-08-28 22:25</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-28 22:25</t>
+          <t>更新时间: 2026-08-28 23:48</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-28 23:48</t>
+          <t>更新时间: 2026-08-29 12:28</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-29 12:28</t>
+          <t>更新时间: 2026-08-29 15:01</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-29 15:01</t>
+          <t>更新时间: 2026-08-29 15:46</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-29 15:46</t>
+          <t>更新时间: 2026-08-29 17:10</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-29 17:10</t>
+          <t>更新时间: 2026-08-29 18:37</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-29 18:37</t>
+          <t>更新时间: 2026-08-30 09:45</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-30 09:45</t>
+          <t>更新时间: 2026-08-30 13:21</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-30 13:21</t>
+          <t>更新时间: 2026-08-30 14:25</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-30 14:25</t>
+          <t>更新时间: 2026-08-30 16:23</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-30 16:23</t>
+          <t>更新时间: 2026-08-30 17:37</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-30 17:37</t>
+          <t>更新时间: 2026-08-31 09:44</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-31 09:44</t>
+          <t>更新时间: 2026-08-31 13:29</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-31 13:29</t>
+          <t>更新时间: 2026-08-31 14:52</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-31 14:52</t>
+          <t>更新时间: 2026-08-31 16:44</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-31 16:44</t>
+          <t>更新时间: 2026-08-31 18:18</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-31 18:18</t>
+          <t>更新时间: 2026-09-01 10:13</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-01 10:13</t>
+          <t>更新时间: 2026-09-01 13:04</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-01 13:04</t>
+          <t>更新时间: 2026-09-01 14:10</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-01 14:10</t>
+          <t>更新时间: 2026-09-01 15:53</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-01 15:53</t>
+          <t>更新时间: 2026-09-01 17:02</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-01 17:02</t>
+          <t>更新时间: 2026-09-02 09:30</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-02 09:30</t>
+          <t>更新时间: 2026-09-02 12:29</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-02 12:29</t>
+          <t>更新时间: 2026-09-02 13:36</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-02 13:36</t>
+          <t>更新时间: 2026-09-02 15:10</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-02 15:10</t>
+          <t>更新时间: 2026-09-02 16:16</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-02 16:16</t>
+          <t>更新时间: 2026-09-03 09:34</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-03 09:34</t>
+          <t>更新时间: 2026-09-03 12:20</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-03 12:20</t>
+          <t>更新时间: 2026-09-03 13:37</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-03 13:37</t>
+          <t>更新时间: 2026-09-03 15:15</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-03 15:15</t>
+          <t>更新时间: 2026-09-03 16:25</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-03 16:25</t>
+          <t>更新时间: 2026-09-04 09:37</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-04 09:37</t>
+          <t>更新时间: 2026-09-04 12:28</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-04 12:28</t>
+          <t>更新时间: 2026-09-04 13:42</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-04 13:42</t>
+          <t>更新时间: 2026-09-04 15:18</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-04 15:18</t>
+          <t>更新时间: 2026-09-04 16:21</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-04 16:21</t>
+          <t>更新时间: 2026-09-05 09:31</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-05 09:31</t>
+          <t>更新时间: 2026-09-05 12:23</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-05 12:23</t>
+          <t>更新时间: 2026-09-05 13:31</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-05 13:31</t>
+          <t>更新时间: 2026-09-05 14:59</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-05 14:59</t>
+          <t>更新时间: 2026-09-05 15:57</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-05 15:57</t>
+          <t>更新时间: 2026-09-06 09:29</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-06 09:29</t>
+          <t>更新时间: 2026-09-06 12:35</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-06 12:35</t>
+          <t>更新时间: 2026-09-06 13:44</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-06 13:44</t>
+          <t>更新时间: 2026-09-06 15:11</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-06 15:11</t>
+          <t>更新时间: 2026-09-06 16:14</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-06 16:14</t>
+          <t>更新时间: 2026-09-07 09:28</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-07 09:28</t>
+          <t>更新时间: 2026-09-07 12:36</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-07 12:36</t>
+          <t>更新时间: 2026-09-07 13:54</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-07 13:54</t>
+          <t>更新时间: 2026-09-07 15:24</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-07 15:24</t>
+          <t>更新时间: 2026-09-07 16:47</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-07 16:47</t>
+          <t>更新时间: 2026-09-08 09:35</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-08 09:35</t>
+          <t>更新时间: 2026-09-08 12:32</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-08 12:32</t>
+          <t>更新时间: 2026-09-08 13:47</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-08 13:47</t>
+          <t>更新时间: 2026-09-08 15:18</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-08 15:18</t>
+          <t>更新时间: 2026-09-08 16:28</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-08 16:28</t>
+          <t>更新时间: 2026-09-09 09:38</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-09 09:38</t>
+          <t>更新时间: 2026-09-09 12:38</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-09 12:38</t>
+          <t>更新时间: 2026-09-09 13:51</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-09 13:51</t>
+          <t>更新时间: 2026-09-09 15:27</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-09 15:27</t>
+          <t>更新时间: 2026-09-09 16:30</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-09 16:30</t>
+          <t>更新时间: 2026-09-10 09:34</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-10 09:34</t>
+          <t>更新时间: 2026-09-10 12:38</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-10 12:38</t>
+          <t>更新时间: 2026-09-10 13:45</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-10 13:45</t>
+          <t>更新时间: 2026-09-10 15:23</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-10 15:23</t>
+          <t>更新时间: 2026-09-10 16:32</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-10 16:32</t>
+          <t>更新时间: 2026-09-11 09:35</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-11 09:35</t>
+          <t>更新时间: 2026-09-11 12:36</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-11 12:36</t>
+          <t>更新时间: 2026-09-11 13:45</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-11 13:45</t>
+          <t>更新时间: 2026-09-11 15:21</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-11 15:21</t>
+          <t>更新时间: 2026-09-11 16:26</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-11 16:26</t>
+          <t>更新时间: 2026-09-12 09:39</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-12 09:39</t>
+          <t>更新时间: 2026-09-12 12:31</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-12 12:31</t>
+          <t>更新时间: 2026-09-12 13:33</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-12 13:33</t>
+          <t>更新时间: 2026-09-12 15:13</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-12 15:13</t>
+          <t>更新时间: 2026-09-12 16:15</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-12 16:15</t>
+          <t>更新时间: 2026-09-13 09:36</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-13 09:36</t>
+          <t>更新时间: 2026-09-13 12:43</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-13 12:43</t>
+          <t>更新时间: 2026-09-13 13:53</t>
         </is>
       </c>
     </row>
